--- a/ttl_long/AdHoc_Net_3.xlsx
+++ b/ttl_long/AdHoc_Net_3.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>51</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>113</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>64</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>341</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>137</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>232</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>170</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>313</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>114</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>185</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>230</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>139</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>205</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>300</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>275</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>240</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>318</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>346</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>371</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>229</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>412</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>327</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>428</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>85</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>493</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>170</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>515</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>310</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>517</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>105</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>583</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>179</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>674</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>336</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>611</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>773</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>105</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>700</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>320</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>764</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>812</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>251</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>876</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>840</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>886</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>238</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>995</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>390</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>909</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>57</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1055</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>263</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1010</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1072</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1209</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>130</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1119</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>333</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1108</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1269</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>126</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1235</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>290</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1239</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,165 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1419</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1528</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1461</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1477</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1499</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1573</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1581</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1693</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D113"/>
+  <dimension ref="A1:D150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1159,7 +1312,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1225,7 +1378,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1247,7 +1400,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1269,7 +1422,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1291,7 +1444,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1308,12 +1461,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1335,7 +1488,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1357,7 +1510,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1379,7 +1532,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1396,12 +1549,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1423,7 +1576,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1445,7 +1598,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1467,7 +1620,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1484,12 +1637,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1511,7 +1664,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,12 +1681,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1555,7 +1708,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1577,7 +1730,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1594,7 +1747,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1616,12 +1769,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1643,7 +1796,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1660,12 +1813,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1682,12 +1835,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1709,7 +1862,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1726,12 +1879,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1753,7 +1906,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1770,12 +1923,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1792,12 +1945,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1814,7 +1967,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1836,12 +1989,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1858,12 +2011,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1880,12 +2033,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1902,12 +2055,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1924,12 +2077,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1946,12 +2099,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1968,12 +2121,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1990,12 +2143,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2012,12 +2165,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2034,12 +2187,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2056,12 +2209,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2078,12 +2231,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2100,12 +2253,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2122,12 +2275,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2144,12 +2297,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2166,12 +2319,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2188,12 +2341,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2210,12 +2363,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2232,12 +2385,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2254,12 +2407,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2276,12 +2429,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2298,12 +2451,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2320,12 +2473,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2342,7 +2495,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2364,12 +2517,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2386,12 +2539,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2408,12 +2561,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2430,12 +2583,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2452,12 +2605,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2474,12 +2627,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2496,12 +2649,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2518,12 +2671,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2540,12 +2693,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2562,12 +2715,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2584,12 +2737,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2606,12 +2759,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2628,12 +2781,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2650,12 +2803,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2672,12 +2825,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2694,12 +2847,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2716,12 +2869,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2738,12 +2891,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2760,12 +2913,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2782,12 +2935,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2804,12 +2957,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2826,12 +2979,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2848,12 +3001,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2870,12 +3023,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2892,12 +3045,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2914,12 +3067,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2936,12 +3089,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2958,12 +3111,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2980,12 +3133,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3002,12 +3155,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3024,12 +3177,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3046,12 +3199,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3068,12 +3221,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3090,12 +3243,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3112,12 +3265,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3134,12 +3287,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3156,12 +3309,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3178,12 +3331,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3200,12 +3353,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3222,12 +3375,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3244,12 +3397,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3266,12 +3419,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3288,12 +3441,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3310,12 +3463,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3332,12 +3485,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3354,12 +3507,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3376,12 +3529,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3398,12 +3551,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3420,12 +3573,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3442,12 +3595,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3464,12 +3617,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3486,12 +3639,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3508,12 +3661,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3530,12 +3683,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3552,12 +3705,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3574,12 +3727,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3596,20 +3749,834 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3658,7 +4625,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -3684,7 +4651,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jamm_powe</t>
+          <t>jamm_power</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/ttl_long/AdHoc_Net_3.xlsx
+++ b/ttl_long/AdHoc_Net_3.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>119</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>76</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>309</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>197</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>190</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>77</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>141</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>191</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>237</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>315</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>230</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>390</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>365</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>336</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>105</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>471</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>439</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>280</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>479</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>547</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>220</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>559</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>330</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>622</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>722</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>172</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>750</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>314</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>785</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>895</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>277</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>911</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>912</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>951</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>216</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>1009</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>1038</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>1145</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>269</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>1047</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>277</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>1117</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1164</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1276</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1283</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1354</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>218</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1299</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1392</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1435</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>143</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1444</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>314</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1516</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>112</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1419</t>
+          <t>1544</t>
         </is>
       </c>
     </row>
@@ -1123,148 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1378</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1528</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1461</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1477</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1499</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1573</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1581</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1693</t>
+          <t>1536</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D150"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1312,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1334,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1378,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1400,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1422,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1444,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1461,12 +1325,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1488,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1510,7 +1374,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1527,12 +1391,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1549,12 +1413,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1576,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1598,7 +1462,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1615,7 +1479,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1637,12 +1501,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1659,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1681,12 +1545,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1708,7 +1572,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1725,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1747,12 +1611,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1769,12 +1633,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1791,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1813,12 +1677,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1835,12 +1699,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1857,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1879,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1901,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1923,12 +1787,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1945,12 +1809,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1967,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1989,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2011,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2033,12 +1897,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2055,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2077,7 +1941,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2099,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2121,12 +1985,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2143,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2165,12 +2029,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2187,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2209,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2231,7 +2095,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2253,12 +2117,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2275,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2297,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2319,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2341,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2363,12 +2227,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2385,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2407,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2429,12 +2293,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2451,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2473,12 +2337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2495,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2517,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2539,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2561,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2583,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2605,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2627,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2649,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2671,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2693,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2715,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2737,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2759,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2781,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2803,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2825,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2847,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2869,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2891,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2913,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2935,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2957,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2979,7 +2843,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3001,12 +2865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3023,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3045,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3067,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3111,12 +2975,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3133,12 +2997,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3155,12 +3019,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3177,12 +3041,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3199,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3221,12 +3085,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3243,12 +3107,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3265,12 +3129,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3287,7 +3151,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3309,12 +3173,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3331,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3353,12 +3217,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3375,12 +3239,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3397,12 +3261,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3419,12 +3283,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3441,12 +3305,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3463,12 +3327,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3485,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3507,12 +3371,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3529,12 +3393,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3551,12 +3415,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3573,7 +3437,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3595,12 +3459,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3617,12 +3481,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3639,12 +3503,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3661,12 +3525,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3683,12 +3547,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3705,12 +3569,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3727,12 +3591,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3749,12 +3613,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3771,12 +3635,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3793,12 +3657,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3815,12 +3679,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3837,12 +3701,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3859,12 +3723,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3881,7 +3745,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3903,12 +3767,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3925,12 +3789,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3939,644 +3803,6 @@
         </is>
       </c>
       <c r="D121" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -4615,7 +3841,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -4625,7 +3851,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -4645,7 +3871,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">

--- a/ttl_long/AdHoc_Net_3.xlsx
+++ b/ttl_long/AdHoc_Net_3.xlsx
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>228</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>295</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>82</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>139</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>108</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>275</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>101</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>172</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>253</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>311</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>324</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>249</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>383</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>149</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>423</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>397</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>449</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>104</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>413</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>492</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>599</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>187</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>685</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>286</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>581</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>830</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>114</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>691</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>327</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>767</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>847</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>207</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>787</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>325</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>856</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>924</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1058</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>319</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1033</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1063</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1144</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1147</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1162</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>181</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1258</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>316</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1237</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>98</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1444</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>176</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1414</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>343</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1408</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1406</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1482</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1461</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1550</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>109</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1578</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1391,12 +1391,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1523,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1721,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1875,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1919,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1941,12 +1941,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1985,12 +1985,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2029,12 +2029,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2051,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2161,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2183,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2249,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2293,12 +2293,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2337,12 +2337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2359,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2381,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2403,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2425,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2447,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2535,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2645,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2689,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2711,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2755,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2777,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2843,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2865,12 +2865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2887,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2909,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2931,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2953,12 +2953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2975,12 +2975,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2997,12 +2997,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3019,12 +3019,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3041,7 +3041,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3063,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3085,12 +3085,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3107,12 +3107,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3151,12 +3151,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3173,12 +3173,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3217,12 +3217,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3239,12 +3239,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3261,12 +3261,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3283,12 +3283,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3305,12 +3305,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3349,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3371,7 +3371,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3393,7 +3393,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3415,12 +3415,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3437,12 +3437,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3459,12 +3459,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3481,12 +3481,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3503,12 +3503,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3525,12 +3525,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3547,12 +3547,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3569,7 +3569,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3591,12 +3591,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3613,196 +3613,20 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="C113" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3841,7 +3665,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -3851,7 +3675,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
